--- a/tables/Monster.xlsx
+++ b/tables/Monster.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.630000000000001" customWidth="1" min="1" max="1"/>
@@ -652,11 +652,6 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
@@ -716,11 +711,6 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
           <t>짚 팔로 잡기</t>
         </is>
       </c>
@@ -780,11 +770,6 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
           <t>돌진 중 슈퍼아머</t>
         </is>
       </c>
@@ -844,11 +829,6 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
           <t>변종: 죽을 때 불 남김, 해체하면 안 남김</t>
         </is>
       </c>
@@ -907,11 +887,6 @@
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>변종</t>
         </is>

--- a/tables/Monster.xlsx
+++ b/tables/Monster.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>AI 종류·시야·공격 거리·대기·공격 목록·체세 회복·해체 방식·슈퍼아머.</t>
+          <t>CSV,AI 종류·시야·공격 거리·대기·공격 목록·체세 회복·해체 방식·슈퍼아머.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/Monster.xlsx
+++ b/tables/Monster.xlsx
@@ -451,10 +451,10 @@
     <col width="6.38" customWidth="1" min="6" max="6"/>
     <col width="6.75" customWidth="1" min="7" max="7"/>
     <col width="37.13" customWidth="1" min="8" max="8"/>
-    <col width="13.75" customWidth="1" min="9" max="9"/>
-    <col width="9.630000000000001" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10.25" customWidth="1" min="12" max="12"/>
+    <col width="9.630000000000001" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10.25" customWidth="1" min="11" max="11"/>
+    <col width="9.880000000000001" customWidth="1" min="12" max="12"/>
     <col width="9.880000000000001" customWidth="1" min="13" max="13"/>
     <col width="21.13" customWidth="1" min="14" max="14"/>
   </cols>
@@ -467,7 +467,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 잡몹 하나의 AI·체세 설정. 스탯은 UnitID로 UnitStat에서 가져옴. AttackIDs는 Attack ID를 | 로 구분.</t>
+          <t>한 행 = 잡몹 하나의 AI·체세 설정. 스탯은 UnitID로 UnitStat에서 가져옴. IdleMin~SuperArmor는 BossState·EliteState와 같은 열·같은 순서(몬스터 공통). ExecuteType KILL이면 ExecuteDamage는 0(즉사). 공격 패턴·배율은 데이터로 두지 않음(Attack 삭제, 10/29).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>CSV,AI 종류·시야·공격 거리·대기·공격 목록·체세 회복·해체 방식·슈퍼아머.</t>
+          <t>CSV,AI 종류·시야·공격 거리·대기·체세 회복·해체 방식·슈퍼아머.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -622,27 +622,27 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>AttackIDs</t>
+          <t>PoiseRegenDelay</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PoiseRegenDelay</t>
+          <t>PoiseRegen</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>PoiseRegen</t>
+          <t>ExposeTime</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>ExposeTime</t>
+          <t>ExecuteType</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>ExecuteType</t>
+          <t>ExecuteDamage</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -685,24 +685,22 @@
       <c r="H7" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>5007|5008</t>
-        </is>
+      <c r="I7" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>KILL</t>
         </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
@@ -744,24 +742,22 @@
       <c r="H8" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>5009|5010</t>
-        </is>
+      <c r="I8" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>KILL</t>
         </is>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -803,24 +799,22 @@
       <c r="H9" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>5007|5008|5011</t>
-        </is>
+      <c r="I9" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>KILL</t>
         </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
@@ -862,24 +856,22 @@
       <c r="H10" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5009|5010|5012</t>
-        </is>
+      <c r="I10" s="3" t="n">
+        <v>2000</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>KILL</t>
         </is>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>

--- a/tables/Monster.xlsx
+++ b/tables/Monster.xlsx
@@ -451,10 +451,10 @@
     <col width="6.38" customWidth="1" min="6" max="6"/>
     <col width="6.75" customWidth="1" min="7" max="7"/>
     <col width="37.13" customWidth="1" min="8" max="8"/>
-    <col width="9.630000000000001" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10.25" customWidth="1" min="11" max="11"/>
-    <col width="9.880000000000001" customWidth="1" min="12" max="12"/>
+    <col width="13.75" customWidth="1" min="9" max="9"/>
+    <col width="9.630000000000001" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10.25" customWidth="1" min="12" max="12"/>
     <col width="9.880000000000001" customWidth="1" min="13" max="13"/>
     <col width="21.13" customWidth="1" min="14" max="14"/>
   </cols>
@@ -597,57 +597,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>IdleMin</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>IdleMax</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseRegenDelay</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseRegen</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ExposeTime</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ExecuteType</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ExecuteDamage</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>AIType</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>SightRange</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>AttackRange</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>IdleMin</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>IdleMax</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>PoiseRegenDelay</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>PoiseRegen</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>ExposeTime</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>ExecuteType</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>ExecuteDamage</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>SuperArmor</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -668,44 +668,44 @@
       <c r="C7" s="3" t="n">
         <v>1002</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MELEE</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>2000</v>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>KILL</t>
+        </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>KILL</t>
+          <t>MELEE</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>800</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>150</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -725,44 +725,44 @@
       <c r="C8" s="3" t="n">
         <v>1003</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>CHARGER</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>2000</v>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>KILL</t>
+        </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>KILL</t>
+          <t>CHARGER</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+        <v>800</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>600</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -782,44 +782,44 @@
       <c r="C9" s="3" t="n">
         <v>1004</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>MELEE</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>2000</v>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>KILL</t>
+        </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>KILL</t>
+          <t>MELEE</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>800</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>150</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -839,44 +839,44 @@
       <c r="C10" s="3" t="n">
         <v>1005</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>CHARGER</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>2000</v>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>KILL</t>
+        </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>KILL</t>
+          <t>CHARGER</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+        <v>800</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>600</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>

--- a/tables/Monster.xlsx
+++ b/tables/Monster.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>짚 팔로 잡기. 지스타: 해체는 보스만(10/30), 잡몹은 체세·급소 노출·해체 없음</t>
+          <t>짚 팔로 잡기. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>돌진 중 슈퍼아머. 지스타: 해체는 보스만(10/30), 잡몹은 체세·급소 노출·해체 없음</t>
+          <t>돌진 중 슈퍼아머. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>변종: 죽을 때 불 남김. 지스타: 해체는 보스만(10/30), 잡몹은 체세·급소 노출·해체 없음</t>
+          <t>변종: 죽을 때 불 남김. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>변종. 지스타: 해체는 보스만(10/30), 잡몹은 체세·급소 노출·해체 없음</t>
+          <t>변종. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
         </is>
       </c>
     </row>

--- a/tables/Monster.xlsx
+++ b/tables/Monster.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>짚 팔로 잡기. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
+          <t>짚 팔로 잡기. 지스타: 잡몹은 체세·해체 없음(보스만), 3~6타에 죽도록 조정. 체세는 구현 단계에서 다시 다듬음(10/30)</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>돌진 중 슈퍼아머. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
+          <t>돌진 중 슈퍼아머. 지스타: 잡몹은 체세·해체 없음(보스만), 3~6타에 죽도록 조정. 체세는 구현 단계에서 다시 다듬음(10/30)</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>변종: 죽을 때 불 남김. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
+          <t>변종: 죽을 때 불 남김. 지스타: 잡몹은 체세·해체 없음(보스만), 3~6타에 죽도록 조정. 체세는 구현 단계에서 다시 다듬음(10/30)</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>변종. 지스타: 해체는 보스만(10/30). 잡몹 체세 0일 때 처리는 확인 중</t>
+          <t>변종. 지스타: 잡몹은 체세·해체 없음(보스만), 3~6타에 죽도록 조정. 체세는 구현 단계에서 다시 다듬음(10/30)</t>
         </is>
       </c>
     </row>
